--- a/docs/機能一覧.xlsx
+++ b/docs/機能一覧.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\0woodyprojects\taskmanager\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C6F9BB-E5B3-409C-A316-FE895F1EBC73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD081DE9-1196-4A3C-9C46-09D7AFA64EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="機能一覧" sheetId="1" r:id="rId1"/>
+    <sheet name="要望（資料収集）" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="150">
   <si>
     <t>No</t>
   </si>
@@ -83,15 +84,9 @@
     <t>TaskClientsテーブル(receiptFolderId/renamedFolderId/uketoriFolderId/senderEmails等を保持し、AIエージェント機能から参照される)</t>
   </si>
   <si>
-    <t>受信したメールを自動で振り分け、保存する。</t>
-  </si>
-  <si>
     <t>受信エージェント</t>
   </si>
   <si>
-    <t>Gmail新着メールを要約し、差出人/転送元/宛先アドレスから関与先を判定して履歴に記録、添付ファイルは関与先のGoogle Drive受領フォルダへ保存する(エージェント名: 受領)</t>
-  </si>
-  <si>
     <t>AgentsPanel.jsx(agent id: scout、名称「受領」) - 指示文を生成しジョブ発行、受領フォルダへのリンクを表示</t>
   </si>
   <si>
@@ -123,9 +118,6 @@
   </si>
   <si>
     <t>TaskClients(senderEmails/uketoriFolderId)、TaskHistory、Gmailラベル「エージェント処理済」、TaskAgentJobsテーブル</t>
-  </si>
-  <si>
-    <t>資料を自動分類し、フォルダ分けして保存される</t>
   </si>
   <si>
     <t>資料分類エージェント</t>
@@ -341,17 +333,7 @@
   </si>
   <si>
     <t>機能拡張できる</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>資料の整理進捗が自動で更新され表示される</t>
-    <rPh sb="0" eb="2">
-      <t>シリョウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>セイリ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>源泉徴収の進捗が管理できる</t>
@@ -364,28 +346,28 @@
     <rPh sb="8" eb="10">
       <t>カンリ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>実装状況</t>
     <rPh sb="2" eb="4">
       <t>ジョウキョウ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>完成</t>
     <rPh sb="0" eb="2">
       <t>カンセイ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>未着手</t>
     <rPh sb="0" eb="3">
       <t>ミチャクシュ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>個人の確定申告の進捗が管理できる</t>
@@ -401,7 +383,7 @@
     <rPh sb="11" eb="13">
       <t>カンリ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>年末調整の進捗が管理できる</t>
@@ -414,14 +396,14 @@
     <rPh sb="8" eb="10">
       <t>カンリ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>源泉タブ</t>
     <rPh sb="0" eb="2">
       <t>ゲンセン</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>年調タブ</t>
@@ -431,14 +413,14 @@
     <rPh sb="1" eb="2">
       <t>チョウ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>個人タブ</t>
     <rPh sb="0" eb="2">
       <t>コジン</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>給与集計、納付書作成の進捗</t>
@@ -451,7 +433,7 @@
     <rPh sb="11" eb="13">
       <t>シンチョク</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>扶養控除申告書、年末調整計算、納付書の進捗</t>
@@ -470,7 +452,7 @@
     <rPh sb="19" eb="21">
       <t>シンチョク</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>確認、申告、報告、納付書、報酬の進捗</t>
@@ -492,7 +474,7 @@
     <rPh sb="16" eb="18">
       <t>シンチョク</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>仕訳入力の管理ができる</t>
@@ -505,7 +487,7 @@
     <rPh sb="5" eb="7">
       <t>カンリ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>自動仕分け作成</t>
@@ -515,14 +497,14 @@
     <rPh sb="5" eb="7">
       <t>サクセイ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>進捗タブ</t>
     <rPh sb="0" eb="2">
       <t>シンチョク</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>仕訳結果を取り込み、進捗を更新する</t>
@@ -544,7 +526,7 @@
     <rPh sb="13" eb="15">
       <t>コウシン</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>仕訳データの作成入力ができる</t>
@@ -557,7 +539,7 @@
     <rPh sb="8" eb="10">
       <t>ニュウリョク</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>範囲外（JDLの範囲）</t>
@@ -567,19 +549,381 @@
     <rPh sb="8" eb="10">
       <t>ハンイ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>As-Is　資料受領</t>
+    <rPh sb="6" eb="8">
+      <t>シリョウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジュリョウ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>顧問先</t>
+    <rPh sb="0" eb="3">
+      <t>コモンサキ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>媒体</t>
+    <rPh sb="0" eb="2">
+      <t>バイタイ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>税理士事務所</t>
+    <rPh sb="0" eb="3">
+      <t>ゼイリシ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ジムショ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>領収書</t>
+    <rPh sb="0" eb="3">
+      <t>リョウシュウショ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>郵送（紙）</t>
+    <rPh sb="0" eb="2">
+      <t>ユウソウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カミ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>担当ごとに</t>
+    <rPh sb="0" eb="2">
+      <t>タントウ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>請求書</t>
+    <rPh sb="0" eb="3">
+      <t>セイキュウショ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>メール</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>個別管理</t>
+    <rPh sb="0" eb="4">
+      <t>コベツカンリ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>預金通帳</t>
+    <rPh sb="0" eb="4">
+      <t>ヨキンツウチョウ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>line</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>給与data</t>
+    <rPh sb="0" eb="2">
+      <t>キュウヨ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>Googleドライブ</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>など</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>チャットワーク</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>To-Be　資料受領とスケジュール管理</t>
+    <rPh sb="6" eb="10">
+      <t>シリョウジュリョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>➡従来通り（またはJDL対応に任せる）</t>
+    <rPh sb="1" eb="4">
+      <t>ジュウライドオ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>マカ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>➡電子媒体でもらい受ける添付ファイルは、着信後自動で
+①顧問先ごとにフォルダ分け
+②ファイル名の置き換え
+③必用書類リストの更新
+④未収集リストの督促メール
+⑤進捗管理表の資料収集部分と連動</t>
+    <rPh sb="1" eb="5">
+      <t>デンシバイタイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>テンプ</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>チャクシンゴ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="28" eb="31">
+      <t>コモンサキ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="54" eb="58">
+      <t>ヒツヨウショルイ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="66" eb="69">
+      <t>ミシュウシュウ</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>トクソク</t>
+    </rPh>
+    <rPh sb="80" eb="84">
+      <t>シンチョクカンリ</t>
+    </rPh>
+    <rPh sb="84" eb="85">
+      <t>ヒョウ</t>
+    </rPh>
+    <rPh sb="86" eb="88">
+      <t>シリョウ</t>
+    </rPh>
+    <rPh sb="88" eb="92">
+      <t>シュウシュウブブン</t>
+    </rPh>
+    <rPh sb="93" eb="95">
+      <t>レンドウ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>➡最終的には収集した資料をJDLに取り込むところも自動化できるか？</t>
+    <rPh sb="1" eb="4">
+      <t>サイシュウテキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シュウシュウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シリョウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>ジドウカ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>↑</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>※本文に直接情報を記載されている場合はどうするか？</t>
+    <rPh sb="1" eb="3">
+      <t>ホンブン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>チョクセツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>一旦は媒体は</t>
+    <rPh sb="0" eb="2">
+      <t>イッタン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>バイタイ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>※これらが可能となるシステム環境と前提となる顧問先や資料マスタにはどんなのもが必要になるか？➡手間と費用感</t>
+    <rPh sb="5" eb="7">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ゼンテイ</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>コモンサキ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>シリョウ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>テマ</t>
+    </rPh>
+    <rPh sb="50" eb="53">
+      <t>ヒヨウカン</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>これだけでOK</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Gmail新着メールを要約し、差出人/転送元/宛先アドレスから関与先を判定して履歴に記録、添付ファイルは関与先のGoogle Drive受領フォルダへ保存する(エージェント名: 受領)
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">②ファイル名の置き換え
+資料を自動分類し、フォルダ分けして保存される
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>③必用書類リストの更新
+⑤進捗管理表の資料収集部分と連動
+資料の整理進捗が自動で更新され表示される</t>
+    <rPh sb="30" eb="32">
+      <t>シリョウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>セイリ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">④未収集リストの督促メール
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>①顧問先ごとにフォルダ分け
+受信したメールを自動で振り分け、保存する。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Googleドライブで受領した資料を振り分け処理する</t>
+    <rPh sb="18" eb="19">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>LINEメッセージを振り分け処理する</t>
+    <rPh sb="10" eb="11">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>チャットワークメッセージを振り分け処理する</t>
+    <rPh sb="13" eb="14">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -597,8 +941,30 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="メイリオ"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="メイリオ"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -620,6 +986,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -672,12 +1050,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -693,6 +1074,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -701,23 +1090,31 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="標準 2" xfId="1" xr:uid="{6FB532B6-0DC1-447F-AB1D-BCE2A8C210B9}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1022,7 +1419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1053,20 +1450,20 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="11">
+      <c r="A2" s="16">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="14" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
@@ -1076,14 +1473,14 @@
         <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
       <c r="E3" s="2" t="s">
         <v>9</v>
       </c>
@@ -1091,14 +1488,14 @@
         <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
       <c r="E4" s="2" t="s">
         <v>12</v>
       </c>
@@ -1106,14 +1503,14 @@
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
@@ -1121,1023 +1518,1233 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+      <c r="A6" s="11">
         <v>2</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="C6" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>18</v>
+      <c r="D6" s="15" t="s">
+        <v>142</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
       <c r="E7" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G7" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="5" t="s">
+      <c r="G8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G8" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="51" x14ac:dyDescent="0.25">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="5" t="s">
+      <c r="G9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G9" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="5" t="s">
+      <c r="G10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="12"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G10" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>28</v>
-      </c>
       <c r="G11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
       <c r="E12" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="6"/>
+      <c r="G13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="6"/>
+      <c r="G14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6"/>
+      <c r="G15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="16">
+        <v>3</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="G12" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="11">
-        <v>3</v>
-      </c>
-      <c r="B13" s="11" t="s">
+      <c r="E16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="G16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="G18" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="G19" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G13" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="G20" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G15" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="51" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="G21" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G16" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="51" x14ac:dyDescent="0.25">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="G22" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="11">
+        <v>4</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="C23" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="G17" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="D23" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="G18" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G19" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
-        <v>4</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G20" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G21" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G22" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
       <c r="E23" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G23" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
       <c r="E24" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G24" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
+      <c r="A25" s="12"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
       <c r="E25" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G25" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
       <c r="E26" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G26" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
       <c r="E27" s="5" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G27" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
       <c r="E28" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G28" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
       <c r="E29" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F29" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G29" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G30" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G31" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="12"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F33" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G29" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="5" t="s">
+      <c r="G33" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="12"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G30" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="5" t="s">
+      <c r="F34" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G34" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A35" s="12"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F35" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G35" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="12"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G36" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="13"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F37" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G31" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="G32" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="G33" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G34" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="13"/>
-      <c r="B35" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="D35" s="13"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="16" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="4">
-        <v>5</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="E36" s="5"/>
-      <c r="F36" s="6"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="4">
-        <v>6</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E37" s="5"/>
-      <c r="F37" s="6"/>
       <c r="G37" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="4">
-        <v>7</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>113</v>
-      </c>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A38" s="4"/>
+      <c r="B38" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
       <c r="E38" s="5"/>
       <c r="F38" s="6"/>
-      <c r="G38" t="s">
+    </row>
+    <row r="39" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="7"/>
+      <c r="B39" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D39" s="7"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="4">
+        <v>5</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E40" s="5"/>
+      <c r="F40" s="6"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="4">
+        <v>6</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E41" s="5"/>
+      <c r="F41" s="6"/>
+      <c r="G41" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="4">
+        <v>7</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C42" s="4" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="4">
+      <c r="D42" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E42" s="5"/>
+      <c r="F42" s="6"/>
+      <c r="G42" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="4">
         <v>8</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B43" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C39" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="E39" s="5"/>
-      <c r="F39" s="6"/>
-      <c r="G39" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="11">
+      <c r="D43" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E43" s="5"/>
+      <c r="F43" s="6"/>
+      <c r="G43" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="7"/>
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="9"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="16">
         <v>9</v>
       </c>
-      <c r="B40" s="11" t="s">
+      <c r="B45" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F45" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="G45" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A46" s="12"/>
+      <c r="B46" s="12"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="10" t="s">
+      <c r="G46" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A47" s="12"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F47" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="G47" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="12"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G48" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A49" s="13"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F40" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G40" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A41" s="8"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="2" t="s">
+      <c r="F49" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G49" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A50" s="11">
+        <v>10</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="D50" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G50" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="12"/>
+      <c r="B51" s="12"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G41" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A42" s="8"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G42" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="8"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G43" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A44" s="9"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G44" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="7">
-        <v>10</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C45" s="12" t="s">
+      <c r="F51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A52" s="12"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F52" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="G52" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A53" s="12"/>
+      <c r="B53" s="12"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E45" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F45" s="6" t="s">
+      <c r="F53" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="G45" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="8"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G46" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="8"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F47" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="G47" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A48" s="8"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="G48" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A49" s="8"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="G49" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="9"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="G50" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="11">
-        <v>21</v>
-      </c>
-      <c r="B51" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C51" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="D51" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G51" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="8"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="G52" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="9"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="G53" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="7">
-        <v>22</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C54" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>81</v>
-      </c>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A54" s="12"/>
+      <c r="B54" s="12"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
       <c r="E54" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F54" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="G54" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A55" s="13"/>
+      <c r="B55" s="13"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G55" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="16">
+        <v>21</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C56" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D56" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G56" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="12"/>
+      <c r="B57" s="12"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G57" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="13"/>
+      <c r="B58" s="13"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G58" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="11">
+        <v>22</v>
+      </c>
+      <c r="B59" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D59" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G59" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="12"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="12"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="G60" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="12"/>
+      <c r="B61" s="12"/>
+      <c r="C61" s="12"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G61" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="13"/>
+      <c r="B62" s="13"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="13"/>
+      <c r="E62" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F62" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="G54" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="8"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F55" s="6" t="s">
+      <c r="G62" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A63" s="16">
+        <v>23</v>
+      </c>
+      <c r="B63" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="G55" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="8"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="5" t="s">
+      <c r="C63" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="D63" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G63" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="102" x14ac:dyDescent="0.25">
+      <c r="A64" s="12"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="12"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F56" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="G56" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="9"/>
-      <c r="B57" s="9"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F57" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="G57" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A58" s="11">
-        <v>23</v>
-      </c>
-      <c r="B58" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="C58" s="10" t="s">
+      <c r="F64" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D58" s="10" t="s">
+      <c r="G64" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="12"/>
+      <c r="B65" s="12"/>
+      <c r="C65" s="12"/>
+      <c r="D65" s="12"/>
+      <c r="E65" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F58" s="3" t="s">
+      <c r="F65" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="G58" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="102" x14ac:dyDescent="0.25">
-      <c r="A59" s="8"/>
-      <c r="B59" s="8"/>
-      <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F59" s="3" t="s">
+      <c r="G65" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A66" s="13"/>
+      <c r="B66" s="13"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="13"/>
+      <c r="E66" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F66" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="G59" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="8"/>
-      <c r="B60" s="8"/>
-      <c r="C60" s="8"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="2" t="s">
+      <c r="G66" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A67" s="11">
+        <v>24</v>
+      </c>
+      <c r="B67" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C67" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="F60" s="3" t="s">
+      <c r="D67" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="G60" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A61" s="9"/>
-      <c r="B61" s="9"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F61" s="3" t="s">
+      <c r="E67" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="G61" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A62" s="7">
-        <v>24</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C62" s="12" t="s">
+      <c r="F67" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D62" s="12" t="s">
+      <c r="G67" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A68" s="12"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="E62" s="5" t="s">
+      <c r="F68" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="F62" s="6" t="s">
+      <c r="G68" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="13"/>
+      <c r="B69" s="13"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="13"/>
+      <c r="E69" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F69" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="G62" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A63" s="8"/>
-      <c r="B63" s="8"/>
-      <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
-      <c r="E63" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="F63" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="G63" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="9"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="9"/>
-      <c r="E64" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G64" t="s">
-        <v>105</v>
+      <c r="G69" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="A6:A12"/>
-    <mergeCell ref="C51:C53"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="C54:C57"/>
-    <mergeCell ref="D58:D61"/>
-    <mergeCell ref="B54:B57"/>
-    <mergeCell ref="C40:C44"/>
-    <mergeCell ref="B45:B50"/>
-    <mergeCell ref="B62:B64"/>
-    <mergeCell ref="D62:D64"/>
-    <mergeCell ref="D54:D57"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="D23:D37"/>
+    <mergeCell ref="A50:A55"/>
+    <mergeCell ref="C63:C66"/>
+    <mergeCell ref="A67:A69"/>
+    <mergeCell ref="B16:B22"/>
+    <mergeCell ref="C67:C69"/>
+    <mergeCell ref="B63:B66"/>
+    <mergeCell ref="A63:A66"/>
+    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="B67:B69"/>
+    <mergeCell ref="D67:D69"/>
+    <mergeCell ref="D59:D62"/>
     <mergeCell ref="D2:D5"/>
-    <mergeCell ref="A13:A19"/>
-    <mergeCell ref="A40:A44"/>
-    <mergeCell ref="C13:C19"/>
-    <mergeCell ref="B40:B44"/>
-    <mergeCell ref="D40:D44"/>
+    <mergeCell ref="A16:A22"/>
+    <mergeCell ref="A45:A49"/>
+    <mergeCell ref="C16:C22"/>
+    <mergeCell ref="B45:B49"/>
+    <mergeCell ref="D45:D49"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="C2:C5"/>
-    <mergeCell ref="C45:C50"/>
-    <mergeCell ref="B51:B53"/>
+    <mergeCell ref="C50:C55"/>
+    <mergeCell ref="B56:B58"/>
     <mergeCell ref="C6:C12"/>
     <mergeCell ref="D6:D12"/>
-    <mergeCell ref="D51:D53"/>
-    <mergeCell ref="A20:A34"/>
-    <mergeCell ref="B20:B34"/>
-    <mergeCell ref="D45:D50"/>
-    <mergeCell ref="D13:D19"/>
-    <mergeCell ref="C20:C34"/>
+    <mergeCell ref="D56:D58"/>
+    <mergeCell ref="A6:A12"/>
+    <mergeCell ref="C56:C58"/>
+    <mergeCell ref="A59:A62"/>
+    <mergeCell ref="C59:C62"/>
+    <mergeCell ref="D63:D66"/>
+    <mergeCell ref="B59:B62"/>
+    <mergeCell ref="C45:C49"/>
+    <mergeCell ref="B50:B55"/>
+    <mergeCell ref="A23:A37"/>
+    <mergeCell ref="B23:B37"/>
+    <mergeCell ref="D50:D55"/>
+    <mergeCell ref="D16:D22"/>
+    <mergeCell ref="C23:C37"/>
     <mergeCell ref="B6:B12"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="D20:D34"/>
-    <mergeCell ref="A45:A50"/>
-    <mergeCell ref="C58:C61"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="B13:B19"/>
-    <mergeCell ref="C62:C64"/>
-    <mergeCell ref="B58:B61"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="A51:A53"/>
   </mergeCells>
-  <phoneticPr fontId="2"/>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A9E5883-57E2-4346-9F0D-EA5A58E8BDF7}">
+  <dimension ref="B1:G18"/>
+  <sheetFormatPr defaultColWidth="9.3984375" defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="3" width="9.3984375" style="17"/>
+    <col min="4" max="4" width="15.796875" style="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.19921875" style="17" customWidth="1"/>
+    <col min="7" max="16384" width="9.3984375" style="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="17" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="17" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D11" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D12" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="F12" s="20"/>
+      <c r="G12" s="17" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D13" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+    </row>
+    <row r="14" spans="2:7" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D14" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+    </row>
+    <row r="15" spans="2:7" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D15" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D16" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D17" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D18" s="17" t="s">
+        <v>141</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E12:F15"/>
+  </mergeCells>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>